--- a/public/template/机组花名册.xlsx
+++ b/public/template/机组花名册.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\repository\watchdog\public\template\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="25600" windowHeight="11630"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="443">
   <si>
     <t>员工号</t>
   </si>
@@ -218,7 +223,7 @@
     <t>石桂平</t>
   </si>
   <si>
-    <t>777:飞行教员A</t>
+    <t>777:F类机长</t>
   </si>
   <si>
     <t>向宇宽</t>
@@ -230,150 +235,162 @@
     <t>陈宇</t>
   </si>
   <si>
+    <t>赵铁锋</t>
+  </si>
+  <si>
+    <t>覃汉志</t>
+  </si>
+  <si>
+    <t>陈良</t>
+  </si>
+  <si>
+    <t>王军锋</t>
+  </si>
+  <si>
+    <t>张鹏</t>
+  </si>
+  <si>
+    <t>张岭</t>
+  </si>
+  <si>
+    <t>季韬</t>
+  </si>
+  <si>
+    <t>单国强</t>
+  </si>
+  <si>
+    <t>何晓东</t>
+  </si>
+  <si>
+    <t>孟庆荣</t>
+  </si>
+  <si>
+    <t>崔建伟</t>
+  </si>
+  <si>
+    <t>唐兴旺</t>
+  </si>
+  <si>
+    <t>马堃锭</t>
+  </si>
+  <si>
+    <t>何兆麒</t>
+  </si>
+  <si>
+    <t>唐龙</t>
+  </si>
+  <si>
+    <t>高炜</t>
+  </si>
+  <si>
+    <t>刘立华</t>
+  </si>
+  <si>
+    <t>王晓龙</t>
+  </si>
+  <si>
+    <t>张吉</t>
+  </si>
+  <si>
+    <t>曹顺强</t>
+  </si>
+  <si>
+    <t>徐弋</t>
+  </si>
+  <si>
+    <t>张勇</t>
+  </si>
+  <si>
+    <t>陈志鹏</t>
+  </si>
+  <si>
+    <t>刘作炫</t>
+  </si>
+  <si>
+    <t>林与非</t>
+  </si>
+  <si>
+    <t>张晟</t>
+  </si>
+  <si>
+    <t>叶世富</t>
+  </si>
+  <si>
+    <t>尚飞</t>
+  </si>
+  <si>
+    <t>颜文彬</t>
+  </si>
+  <si>
+    <t>谢先正</t>
+  </si>
+  <si>
+    <t>杨奇明</t>
+  </si>
+  <si>
     <t>许伟东</t>
   </si>
   <si>
+    <t>777:E类机长</t>
+  </si>
+  <si>
     <t>梁志龙</t>
   </si>
   <si>
-    <t>赵铁锋</t>
+    <t>闫珺熠</t>
+  </si>
+  <si>
+    <t>张佳霖</t>
+  </si>
+  <si>
+    <t>宾恩辉</t>
+  </si>
+  <si>
+    <t>冀文龙</t>
+  </si>
+  <si>
+    <t>薛杨</t>
+  </si>
+  <si>
+    <t>罗建勇</t>
+  </si>
+  <si>
+    <t>张宇强</t>
+  </si>
+  <si>
+    <t>汤光磊</t>
+  </si>
+  <si>
+    <t>孙玉虎</t>
+  </si>
+  <si>
+    <t>罗竣艺</t>
+  </si>
+  <si>
+    <t>方建斌</t>
+  </si>
+  <si>
+    <t>张琪</t>
+  </si>
+  <si>
+    <t>王佳楠</t>
+  </si>
+  <si>
+    <t>丁汀</t>
+  </si>
+  <si>
+    <t>罗显涛</t>
   </si>
   <si>
     <t>邢晓楠</t>
   </si>
   <si>
-    <t>覃汉志</t>
-  </si>
-  <si>
-    <t>陈良</t>
-  </si>
-  <si>
-    <t>王军锋</t>
-  </si>
-  <si>
-    <t>张鹏</t>
-  </si>
-  <si>
-    <t>张岭</t>
-  </si>
-  <si>
-    <t>季韬</t>
-  </si>
-  <si>
-    <t>单国强</t>
-  </si>
-  <si>
-    <t>何晓东</t>
-  </si>
-  <si>
-    <t>孟庆荣</t>
-  </si>
-  <si>
-    <t>崔建伟</t>
-  </si>
-  <si>
-    <t>唐兴旺</t>
-  </si>
-  <si>
-    <t>马堃锭</t>
-  </si>
-  <si>
-    <t>何兆麒</t>
-  </si>
-  <si>
-    <t>唐龙</t>
-  </si>
-  <si>
-    <t>高炜</t>
-  </si>
-  <si>
-    <t>刘立华</t>
-  </si>
-  <si>
-    <t>王晓龙</t>
-  </si>
-  <si>
-    <t>张吉</t>
-  </si>
-  <si>
-    <t>闫珺熠</t>
-  </si>
-  <si>
-    <t>张佳霖</t>
-  </si>
-  <si>
-    <t>曹顺强</t>
-  </si>
-  <si>
-    <t>宾恩辉</t>
-  </si>
-  <si>
-    <t>徐弋</t>
-  </si>
-  <si>
-    <t>冀文龙</t>
-  </si>
-  <si>
-    <t>张勇</t>
-  </si>
-  <si>
-    <t>陈志鹏</t>
-  </si>
-  <si>
-    <t>刘作炫</t>
-  </si>
-  <si>
-    <t>薛杨</t>
-  </si>
-  <si>
-    <t>罗建勇</t>
-  </si>
-  <si>
-    <t>林与非</t>
-  </si>
-  <si>
-    <t>张晟</t>
-  </si>
-  <si>
-    <t>叶世富</t>
-  </si>
-  <si>
-    <t>尚飞</t>
-  </si>
-  <si>
-    <t>张宇强</t>
-  </si>
-  <si>
-    <t>汤光磊</t>
-  </si>
-  <si>
-    <t>孙玉虎</t>
-  </si>
-  <si>
-    <t>罗竣艺</t>
-  </si>
-  <si>
-    <t>方建斌</t>
-  </si>
-  <si>
-    <t>张琪</t>
-  </si>
-  <si>
-    <t>王佳楠</t>
-  </si>
-  <si>
-    <t>丁汀</t>
-  </si>
-  <si>
-    <t>罗显涛</t>
+    <t>777:D类机长</t>
   </si>
   <si>
     <t>Jochen Etienne L DE WISPELAERE</t>
   </si>
   <si>
-    <t>777:D类机长</t>
-  </si>
-  <si>
     <t>Jan HRASKO</t>
   </si>
   <si>
@@ -407,6 +424,9 @@
     <t>卢晋勋</t>
   </si>
   <si>
+    <t>姚望</t>
+  </si>
+  <si>
     <t>陶炼</t>
   </si>
   <si>
@@ -626,33 +646,45 @@
     <t>盛况</t>
   </si>
   <si>
+    <t>徐海锋</t>
+  </si>
+  <si>
+    <t>覃文添</t>
+  </si>
+  <si>
+    <t>贺万强</t>
+  </si>
+  <si>
+    <t>陈玺</t>
+  </si>
+  <si>
+    <t>姚剑鸣</t>
+  </si>
+  <si>
+    <t>汪杨</t>
+  </si>
+  <si>
+    <t>马勇</t>
+  </si>
+  <si>
+    <t>崔玉柱</t>
+  </si>
+  <si>
     <t>777:Z类机长</t>
   </si>
   <si>
-    <t>崔玉柱</t>
-  </si>
-  <si>
     <t>周思宁</t>
   </si>
   <si>
     <t>王尧</t>
   </si>
   <si>
-    <t>马勇</t>
-  </si>
-  <si>
     <t>白永亮</t>
   </si>
   <si>
     <t>卢彦来</t>
   </si>
   <si>
-    <t>姚剑鸣</t>
-  </si>
-  <si>
-    <t>贺万强</t>
-  </si>
-  <si>
     <t>张亚朋</t>
   </si>
   <si>
@@ -662,9 +694,6 @@
     <t>武中杰</t>
   </si>
   <si>
-    <t>陈玺</t>
-  </si>
-  <si>
     <t>程熊</t>
   </si>
   <si>
@@ -674,12 +703,6 @@
     <t>田权龙</t>
   </si>
   <si>
-    <t>徐海锋</t>
-  </si>
-  <si>
-    <t>覃文添</t>
-  </si>
-  <si>
     <t>吴智鑫</t>
   </si>
   <si>
@@ -692,6 +715,9 @@
     <t>刘宇</t>
   </si>
   <si>
+    <t>SHIM JAE HOON</t>
+  </si>
+  <si>
     <t>王靖江</t>
   </si>
   <si>
@@ -734,6 +760,15 @@
     <t>黄俊豪</t>
   </si>
   <si>
+    <t>任泽尧</t>
+  </si>
+  <si>
+    <t>王瑞丰</t>
+  </si>
+  <si>
+    <t>傅燧旭</t>
+  </si>
+  <si>
     <t>沙思丞</t>
   </si>
   <si>
@@ -749,9 +784,6 @@
     <t>袁珂</t>
   </si>
   <si>
-    <t>傅燧旭</t>
-  </si>
-  <si>
     <t>陈伯楠</t>
   </si>
   <si>
@@ -767,18 +799,12 @@
     <t>温健</t>
   </si>
   <si>
-    <t>任泽尧</t>
-  </si>
-  <si>
     <t>刘信</t>
   </si>
   <si>
     <t>彭田</t>
   </si>
   <si>
-    <t>王瑞丰</t>
-  </si>
-  <si>
     <t>胡金鑫</t>
   </si>
   <si>
@@ -824,15 +850,30 @@
     <t>张义涛</t>
   </si>
   <si>
+    <t>黄磊</t>
+  </si>
+  <si>
+    <t>万木春</t>
+  </si>
+  <si>
+    <t>梁华杨</t>
+  </si>
+  <si>
+    <t>车有路</t>
+  </si>
+  <si>
+    <t>朱戈昊</t>
+  </si>
+  <si>
+    <t>周锐豪</t>
+  </si>
+  <si>
     <t>陈兆铭</t>
   </si>
   <si>
     <t>777:B类副驾驶</t>
   </si>
   <si>
-    <t>周锐豪</t>
-  </si>
-  <si>
     <t>刘洋</t>
   </si>
   <si>
@@ -860,15 +901,9 @@
     <t>崔书宝</t>
   </si>
   <si>
-    <t>车有路</t>
-  </si>
-  <si>
     <t>邓汉昕</t>
   </si>
   <si>
-    <t>万木春</t>
-  </si>
-  <si>
     <t>肖剑鹏</t>
   </si>
   <si>
@@ -881,21 +916,12 @@
     <t>卢勇成</t>
   </si>
   <si>
-    <t>梁华杨</t>
-  </si>
-  <si>
     <t>白帆</t>
   </si>
   <si>
-    <t>朱戈昊</t>
-  </si>
-  <si>
     <t>刘育辰</t>
   </si>
   <si>
-    <t>黄磊</t>
-  </si>
-  <si>
     <t>章辉</t>
   </si>
   <si>
@@ -968,6 +994,33 @@
     <t>朱灿仪</t>
   </si>
   <si>
+    <t>张小康</t>
+  </si>
+  <si>
+    <t>张鑫豪</t>
+  </si>
+  <si>
+    <t>刘智博</t>
+  </si>
+  <si>
+    <t>杨登科</t>
+  </si>
+  <si>
+    <t>杨大锋</t>
+  </si>
+  <si>
+    <t>王年鹏</t>
+  </si>
+  <si>
+    <t>薛力文</t>
+  </si>
+  <si>
+    <t>彭雪峰</t>
+  </si>
+  <si>
+    <t>戴永康</t>
+  </si>
+  <si>
     <t>杨帮翔</t>
   </si>
   <si>
@@ -980,9 +1033,6 @@
     <t>任文煜</t>
   </si>
   <si>
-    <t>刘智博</t>
-  </si>
-  <si>
     <t>薛京亮</t>
   </si>
   <si>
@@ -992,9 +1042,6 @@
     <t>陈子其</t>
   </si>
   <si>
-    <t>张鑫豪</t>
-  </si>
-  <si>
     <t>蒋佩霖</t>
   </si>
   <si>
@@ -1004,15 +1051,6 @@
     <t>胡雨辰</t>
   </si>
   <si>
-    <t>杨登科</t>
-  </si>
-  <si>
-    <t>薛力文</t>
-  </si>
-  <si>
-    <t>张小康</t>
-  </si>
-  <si>
     <t>唐选尧</t>
   </si>
   <si>
@@ -1034,15 +1072,9 @@
     <t>蒋元成</t>
   </si>
   <si>
-    <t>杨大锋</t>
-  </si>
-  <si>
     <t>王金宇</t>
   </si>
   <si>
-    <t>彭雪峰</t>
-  </si>
-  <si>
     <t>朱丹浩</t>
   </si>
   <si>
@@ -1073,12 +1105,6 @@
     <t>袁英杰</t>
   </si>
   <si>
-    <t>王年鹏</t>
-  </si>
-  <si>
-    <t>戴永康</t>
-  </si>
-  <si>
     <t>刘千里</t>
   </si>
   <si>
@@ -1133,18 +1159,39 @@
     <t>于鄢龙</t>
   </si>
   <si>
+    <t>张釜浩</t>
+  </si>
+  <si>
+    <t>苏晓文</t>
+  </si>
+  <si>
     <t>闫文平</t>
   </si>
   <si>
+    <t>王熠铭</t>
+  </si>
+  <si>
+    <t>田庭</t>
+  </si>
+  <si>
+    <t>朱慕杰</t>
+  </si>
+  <si>
+    <t>陈坤淋</t>
+  </si>
+  <si>
+    <t>罗飞</t>
+  </si>
+  <si>
+    <t>杨世榕</t>
+  </si>
+  <si>
+    <t>周国正</t>
+  </si>
+  <si>
     <t>777:A1类副驾驶</t>
   </si>
   <si>
-    <t>王熠铭</t>
-  </si>
-  <si>
-    <t>周国正</t>
-  </si>
-  <si>
     <t>郑杰</t>
   </si>
   <si>
@@ -1157,30 +1204,9 @@
     <t>米磊</t>
   </si>
   <si>
-    <t>张釜浩</t>
-  </si>
-  <si>
     <t>叶科兴</t>
   </si>
   <si>
-    <t>罗飞</t>
-  </si>
-  <si>
-    <t>陈坤淋</t>
-  </si>
-  <si>
-    <t>田庭</t>
-  </si>
-  <si>
-    <t>苏晓文</t>
-  </si>
-  <si>
-    <t>杨世榕</t>
-  </si>
-  <si>
-    <t>朱慕杰</t>
-  </si>
-  <si>
     <t>聂莘欣</t>
   </si>
   <si>
@@ -1211,52 +1237,94 @@
     <t>杨宇轩</t>
   </si>
   <si>
+    <t>李昊轩</t>
+  </si>
+  <si>
+    <t>李劲彧</t>
+  </si>
+  <si>
+    <t>马鸿博</t>
+  </si>
+  <si>
+    <t>彭浩</t>
+  </si>
+  <si>
+    <t>任浩翔</t>
+  </si>
+  <si>
     <t>熊涛</t>
   </si>
   <si>
+    <t>时浩源</t>
+  </si>
+  <si>
+    <t>张展源</t>
+  </si>
+  <si>
+    <t>罗一凡</t>
+  </si>
+  <si>
+    <t>湛怀福</t>
+  </si>
+  <si>
+    <t>李旭</t>
+  </si>
+  <si>
+    <t>杨震</t>
+  </si>
+  <si>
+    <t>刘权</t>
+  </si>
+  <si>
+    <t>丁宇</t>
+  </si>
+  <si>
+    <t>周号</t>
+  </si>
+  <si>
+    <t>刘晋鹏</t>
+  </si>
+  <si>
+    <t>张得喜</t>
+  </si>
+  <si>
+    <t>尤致衡</t>
+  </si>
+  <si>
+    <t>刘瀚阳</t>
+  </si>
+  <si>
     <t>划转副驾驶</t>
   </si>
   <si>
-    <t>时浩源</t>
-  </si>
-  <si>
-    <t>张展源</t>
-  </si>
-  <si>
-    <t>罗一凡</t>
-  </si>
-  <si>
-    <t>湛怀福</t>
-  </si>
-  <si>
-    <t>李旭</t>
-  </si>
-  <si>
-    <t>杨震</t>
-  </si>
-  <si>
-    <t>刘权</t>
-  </si>
-  <si>
-    <t>SHIM JAE HOON</t>
+    <t>张一帆</t>
+  </si>
+  <si>
+    <t>杜雨恒</t>
+  </si>
+  <si>
+    <t>胡安杰</t>
+  </si>
+  <si>
+    <t>季望能</t>
+  </si>
+  <si>
+    <t>刘瑞奇</t>
+  </si>
+  <si>
+    <t>马崇</t>
+  </si>
+  <si>
+    <t>朱春期</t>
   </si>
   <si>
     <t>划转机长</t>
   </si>
   <si>
-    <t>李昊轩</t>
-  </si>
-  <si>
-    <t>李劲彧</t>
-  </si>
-  <si>
-    <t>马鸿博</t>
-  </si>
-  <si>
-    <t>彭浩</t>
-  </si>
-  <si>
-    <t>任浩翔</t>
+    <t>惠晓飞</t>
+  </si>
+  <si>
+    <t>邓超</t>
   </si>
   <si>
     <t>905172</t>
@@ -1265,73 +1333,34 @@
     <t>唐杰斌</t>
   </si>
   <si>
+    <t>刘丹</t>
+  </si>
+  <si>
     <t>张家豪</t>
   </si>
   <si>
-    <t>刘瀚阳</t>
-  </si>
-  <si>
-    <t>张一帆</t>
-  </si>
-  <si>
-    <t>杜雨恒</t>
-  </si>
-  <si>
-    <t>胡安杰</t>
-  </si>
-  <si>
-    <t>季望能</t>
-  </si>
-  <si>
-    <t>朱春期</t>
-  </si>
-  <si>
-    <t>杨奇明</t>
-  </si>
-  <si>
-    <t>颜文彬</t>
-  </si>
-  <si>
-    <t>谢先正</t>
-  </si>
-  <si>
-    <t>姚望</t>
-  </si>
-  <si>
-    <t>汪杨</t>
-  </si>
-  <si>
-    <t>刘瑞奇</t>
-  </si>
-  <si>
-    <t>刘丹</t>
-  </si>
-  <si>
-    <t>丁宇</t>
-  </si>
-  <si>
-    <t>周号</t>
-  </si>
-  <si>
-    <t>马崇</t>
-  </si>
-  <si>
-    <t>张得喜</t>
-  </si>
-  <si>
-    <t>刘晋鹏</t>
-  </si>
-  <si>
-    <t>尤致衡</t>
-  </si>
-  <si>
-    <t>惠晓飞</t>
-  </si>
-  <si>
-    <t>邓超</t>
-  </si>
-  <si>
     <t>熊鑫</t>
+  </si>
+  <si>
+    <t>吴熙泰</t>
+  </si>
+  <si>
+    <t>龚建霆</t>
+  </si>
+  <si>
+    <t>马琰珺</t>
+  </si>
+  <si>
+    <t>黄文渊</t>
+  </si>
+  <si>
+    <t>吕航</t>
+  </si>
+  <si>
+    <t>黄楠</t>
+  </si>
+  <si>
+    <t>WILLIAMS NICOLAS FRASER</t>
   </si>
 </sst>
 </file>
@@ -1344,7 +1373,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1384,6 +1413,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="方正仿宋_GBK"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="方正仿宋_GBK"/>
       <charset val="134"/>
     </font>
@@ -1532,12 +1567,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1867,16 +1914,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1885,58 +1929,55 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1945,10 +1986,10 @@
     <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1957,10 +1998,10 @@
     <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1969,10 +2010,10 @@
     <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1981,10 +2022,10 @@
     <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1993,11 +2034,17 @@
     <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2030,6 +2077,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2563,7 +2619,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D412"/>
+  <dimension ref="A1:D419"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="15.6272727272727" style="1" customWidth="1"/>
@@ -3371,13 +3427,13 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="5">
-        <v>181503</v>
+        <v>181558</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>67</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>63</v>
@@ -3385,13 +3441,13 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="5">
-        <v>181513</v>
+        <v>186662</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>63</v>
@@ -3399,13 +3455,13 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="5">
-        <v>181558</v>
+        <v>193391</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>69</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>63</v>
@@ -3413,7 +3469,7 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="5">
-        <v>181727</v>
+        <v>201906</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>70</v>
@@ -3427,13 +3483,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="5">
-        <v>186662</v>
+        <v>202990</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>71</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>63</v>
@@ -3441,13 +3497,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="5">
-        <v>193391</v>
+        <v>901768</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>72</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>63</v>
@@ -3455,13 +3511,13 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="5">
-        <v>201906</v>
+        <v>201982</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>63</v>
@@ -3469,7 +3525,7 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="5">
-        <v>202990</v>
+        <v>905175</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>74</v>
@@ -3483,13 +3539,13 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="5">
-        <v>901768</v>
+        <v>901449</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>75</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>63</v>
@@ -3497,7 +3553,7 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="5">
-        <v>201982</v>
+        <v>181798</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>76</v>
@@ -3511,13 +3567,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="5">
-        <v>905175</v>
+        <v>187952</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>77</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>63</v>
@@ -3525,13 +3581,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="5">
-        <v>901449</v>
+        <v>196520</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>78</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>63</v>
@@ -3539,7 +3595,7 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="5">
-        <v>181798</v>
+        <v>213485</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>79</v>
@@ -3553,13 +3609,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="5">
-        <v>187952</v>
+        <v>212801</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>80</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>63</v>
@@ -3567,41 +3623,41 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="5">
-        <v>196520</v>
+        <v>189182</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>81</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="5">
-        <v>213485</v>
-      </c>
-      <c r="B73" s="6" t="s">
+      <c r="A73" s="9">
+        <v>198207</v>
+      </c>
+      <c r="B73" s="9" t="s">
         <v>82</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="5">
-        <v>212801</v>
-      </c>
-      <c r="B74" s="6" t="s">
+      <c r="A74" s="9">
+        <v>204821</v>
+      </c>
+      <c r="B74" s="9" t="s">
         <v>83</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>63</v>
@@ -3609,23 +3665,23 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="5">
-        <v>189182</v>
+        <v>216861</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>84</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="9">
-        <v>198207</v>
-      </c>
-      <c r="B76" s="9" t="s">
+      <c r="A76" s="5">
+        <v>210252</v>
+      </c>
+      <c r="B76" s="6" t="s">
         <v>85</v>
       </c>
       <c r="C76" s="7" t="s">
@@ -3636,14 +3692,14 @@
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="9">
-        <v>204821</v>
-      </c>
-      <c r="B77" s="9" t="s">
+      <c r="A77" s="8">
+        <v>202368</v>
+      </c>
+      <c r="B77" s="8" t="s">
         <v>86</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>63</v>
@@ -3651,7 +3707,7 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="5">
-        <v>216861</v>
+        <v>186643</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>87</v>
@@ -3665,23 +3721,23 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="5">
-        <v>210252</v>
+        <v>181851</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>88</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="5">
-        <v>216502</v>
-      </c>
-      <c r="B80" s="6" t="s">
+      <c r="A80" s="9">
+        <v>183002</v>
+      </c>
+      <c r="B80" s="10" t="s">
         <v>89</v>
       </c>
       <c r="C80" s="7" t="s">
@@ -3692,24 +3748,24 @@
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="5">
-        <v>214335</v>
-      </c>
-      <c r="B81" s="6" t="s">
+      <c r="A81" s="9">
+        <v>207285</v>
+      </c>
+      <c r="B81" s="10" t="s">
         <v>90</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="8">
-        <v>202368</v>
-      </c>
-      <c r="B82" s="8" t="s">
+      <c r="A82" s="9">
+        <v>208732</v>
+      </c>
+      <c r="B82" s="10" t="s">
         <v>91</v>
       </c>
       <c r="C82" s="7" t="s">
@@ -3720,24 +3776,24 @@
       </c>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="5">
-        <v>215055</v>
-      </c>
-      <c r="B83" s="6" t="s">
+      <c r="A83" s="9">
+        <v>198204</v>
+      </c>
+      <c r="B83" s="10" t="s">
         <v>92</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="5">
-        <v>186643</v>
-      </c>
-      <c r="B84" s="6" t="s">
+      <c r="A84" s="9">
+        <v>207623</v>
+      </c>
+      <c r="B84" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C84" s="7" t="s">
@@ -3748,28 +3804,28 @@
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="5">
-        <v>206748</v>
-      </c>
-      <c r="B85" s="6" t="s">
+      <c r="A85" s="9">
+        <v>213174</v>
+      </c>
+      <c r="B85" s="10" t="s">
         <v>94</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="5">
-        <v>181851</v>
-      </c>
-      <c r="B86" s="6" t="s">
+      <c r="A86" s="9">
+        <v>181737</v>
+      </c>
+      <c r="B86" s="10" t="s">
         <v>95</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>63</v>
@@ -3777,13 +3833,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="9">
-        <v>183002</v>
+        <v>205160</v>
       </c>
       <c r="B87" s="10" t="s">
         <v>96</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>63</v>
@@ -3791,7 +3847,7 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="9">
-        <v>207285</v>
+        <v>181642</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>97</v>
@@ -3804,246 +3860,246 @@
       </c>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="6">
-        <v>901714</v>
+      <c r="A89" s="5">
+        <v>181503</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>98</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="9">
-        <v>202417</v>
-      </c>
-      <c r="B90" s="10" t="s">
+      <c r="A90" s="5">
+        <v>181513</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D90" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C90" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>63</v>
-      </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="9">
-        <v>208732</v>
-      </c>
-      <c r="B91" s="10" t="s">
-        <v>100</v>
+      <c r="A91" s="5">
+        <v>216502</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="9">
-        <v>198204</v>
-      </c>
-      <c r="B92" s="10" t="s">
-        <v>101</v>
+      <c r="A92" s="5">
+        <v>214335</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="9">
-        <v>207623</v>
-      </c>
-      <c r="B93" s="10" t="s">
-        <v>102</v>
+      <c r="A93" s="5">
+        <v>215055</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="C93" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="9">
-        <v>213174</v>
-      </c>
-      <c r="B94" s="10" t="s">
-        <v>103</v>
+      <c r="A94" s="5">
+        <v>206748</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95" s="9">
-        <v>901785</v>
-      </c>
-      <c r="B95" s="10" t="s">
-        <v>104</v>
+      <c r="A95" s="6">
+        <v>901714</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="9">
+        <v>202417</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="9">
+        <v>901785</v>
+      </c>
+      <c r="B97" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="9">
         <v>181688</v>
       </c>
-      <c r="B96" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="8">
+      <c r="B98" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="8">
         <v>901621</v>
       </c>
-      <c r="B97" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="5">
-        <v>210239</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="9">
-        <v>186663</v>
-      </c>
-      <c r="B99" s="10" t="s">
-        <v>108</v>
+      <c r="B99" s="8" t="s">
+        <v>109</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="5">
-        <v>207621</v>
+        <v>210239</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101" spans="1:4">
-      <c r="A101" s="6">
-        <v>216750</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>110</v>
+      <c r="A101" s="9">
+        <v>186663</v>
+      </c>
+      <c r="B101" s="10" t="s">
+        <v>111</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="5">
+        <v>207621</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="6">
+        <v>216750</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="5">
         <v>210227</v>
       </c>
-      <c r="B102" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D102" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="9">
-        <v>201138</v>
-      </c>
-      <c r="B103" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="104" ht="42" spans="1:4">
-      <c r="A104" s="9">
-        <v>777575</v>
-      </c>
-      <c r="B104" s="10" t="s">
-        <v>113</v>
+      <c r="B104" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="9">
-        <v>771602</v>
+        <v>201138</v>
       </c>
       <c r="B105" s="10" t="s">
         <v>115</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="5">
-        <v>215610</v>
+        <v>181727</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>116</v>
@@ -4052,1188 +4108,1188 @@
         <v>13</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="107" ht="42" spans="1:4">
       <c r="A107" s="9">
+        <v>777575</v>
+      </c>
+      <c r="B107" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="9">
+        <v>771602</v>
+      </c>
+      <c r="B108" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="5">
+        <v>215610</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="9">
         <v>213091</v>
       </c>
-      <c r="B107" s="10" t="s">
+      <c r="B110" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="5">
-        <v>213107</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="9">
-        <v>901531</v>
-      </c>
-      <c r="B109" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="5">
-        <v>216505</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="5">
-        <v>210899</v>
+        <v>213107</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C111" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="112" spans="1:4">
-      <c r="A112" s="6">
-        <v>215060</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>122</v>
+      <c r="A112" s="9">
+        <v>901531</v>
+      </c>
+      <c r="B112" s="10" t="s">
+        <v>123</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="5">
-        <v>216757</v>
+        <v>216505</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="5">
-        <v>208978</v>
+        <v>210899</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="115" spans="1:4">
-      <c r="A115" s="5">
-        <v>212914</v>
+      <c r="A115" s="6">
+        <v>215060</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="5">
-        <v>210510</v>
+        <v>216757</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="5">
-        <v>193177</v>
+        <v>208978</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>128</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="5">
-        <v>202989</v>
+        <v>212914</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>129</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="119" spans="1:4">
-      <c r="A119" s="5">
-        <v>208984</v>
-      </c>
-      <c r="B119" s="6" t="s">
+      <c r="A119" s="9">
+        <v>212794</v>
+      </c>
+      <c r="B119" s="10" t="s">
         <v>130</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="5">
-        <v>212810</v>
+        <v>210510</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>131</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="5">
-        <v>184767</v>
+        <v>193177</v>
       </c>
       <c r="B121" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D121" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="5">
-        <v>193238</v>
+        <v>202989</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="5">
-        <v>196015</v>
+        <v>208984</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="5">
-        <v>206751</v>
+        <v>212810</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C124" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="5">
-        <v>193002</v>
+        <v>184767</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="5">
-        <v>209990</v>
+        <v>193238</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="5">
-        <v>212934</v>
+        <v>196015</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="5">
-        <v>196557</v>
+        <v>206751</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="5">
-        <v>211303</v>
+        <v>193002</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="5">
-        <v>212946</v>
+        <v>209990</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="5">
-        <v>708722</v>
+        <v>212934</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="5">
-        <v>210782</v>
+        <v>196557</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="5">
-        <v>210123</v>
+        <v>211303</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="5">
-        <v>211566</v>
+        <v>212946</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="5">
-        <v>202057</v>
+        <v>708722</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="5">
-        <v>211509</v>
+        <v>210782</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="5">
-        <v>207632</v>
+        <v>210123</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="5">
+        <v>211566</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="5">
+        <v>202057</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="5">
+        <v>211509</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="5">
+        <v>207632</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="5">
         <v>189969</v>
       </c>
-      <c r="B138" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C138" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D138" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
-      <c r="A139" s="8">
+      <c r="B142" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="8">
         <v>211542</v>
       </c>
-      <c r="B139" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C139" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D139" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4">
-      <c r="A140" s="8">
+      <c r="B143" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="8">
         <v>612061</v>
       </c>
-      <c r="B140" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="C140" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D140" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4">
-      <c r="A141" s="6">
+      <c r="B144" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="6">
         <v>215056</v>
       </c>
-      <c r="B141" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C141" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D141" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
-      <c r="A142" s="6">
+      <c r="B145" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="6">
         <v>224079</v>
       </c>
-      <c r="B142" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C142" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D142" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
-      <c r="A143" s="5">
+      <c r="B146" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="5">
         <v>218326</v>
       </c>
-      <c r="B143" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C143" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D143" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4">
-      <c r="A144" s="9">
+      <c r="B147" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="9">
         <v>611893</v>
       </c>
-      <c r="B144" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="C144" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D144" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="145" ht="42" spans="1:4">
-      <c r="A145" s="9">
+      <c r="B148" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="149" ht="42" spans="1:4">
+      <c r="A149" s="9">
         <v>263574</v>
       </c>
-      <c r="B145" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="C145" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D145" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4">
-      <c r="A146" s="9">
+      <c r="B149" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="9">
         <v>181594</v>
       </c>
-      <c r="B146" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="C146" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D146" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4">
-      <c r="A147" s="9">
+      <c r="B150" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="9">
         <v>196312</v>
       </c>
-      <c r="B147" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="C147" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D147" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4">
-      <c r="A148" s="6">
-        <v>211590</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C148" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4">
-      <c r="A149" s="5">
-        <v>192425</v>
-      </c>
-      <c r="B149" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C149" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D149" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4">
-      <c r="A150" s="6">
-        <v>212660</v>
-      </c>
-      <c r="B150" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C150" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D150" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4">
-      <c r="A151" s="5">
-        <v>212871</v>
-      </c>
-      <c r="B151" s="6" t="s">
-        <v>162</v>
+      <c r="B151" s="10" t="s">
+        <v>163</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="6">
-        <v>206950</v>
+        <v>211590</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="5">
-        <v>209259</v>
+        <v>192425</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="154" ht="28" spans="1:4">
-      <c r="A154" s="9">
-        <v>248809</v>
-      </c>
-      <c r="B154" s="10" t="s">
-        <v>165</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="6">
+        <v>212660</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>166</v>
       </c>
       <c r="C154" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="155" spans="1:4">
-      <c r="A155" s="9">
-        <v>213078</v>
-      </c>
-      <c r="B155" s="10" t="s">
-        <v>166</v>
+      <c r="A155" s="5">
+        <v>212871</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="6">
-        <v>217555</v>
+        <v>206950</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C156" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="157" spans="1:4">
-      <c r="A157" s="6">
-        <v>206324</v>
+      <c r="A157" s="5">
+        <v>209259</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4">
-      <c r="A158" s="5">
-        <v>217117</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>169</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="158" ht="28" spans="1:4">
+      <c r="A158" s="9">
+        <v>248809</v>
+      </c>
+      <c r="B158" s="10" t="s">
+        <v>170</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="9">
-        <v>901500</v>
+        <v>213078</v>
       </c>
       <c r="B159" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="160" spans="1:4">
-      <c r="A160" s="5">
-        <v>195814</v>
+      <c r="A160" s="6">
+        <v>217555</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="161" spans="1:4">
-      <c r="A161" s="5">
-        <v>225674</v>
+      <c r="A161" s="6">
+        <v>206324</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="5">
-        <v>186664</v>
+        <v>217117</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="163" spans="1:4">
-      <c r="A163" s="5">
-        <v>234426</v>
-      </c>
-      <c r="B163" s="6" t="s">
-        <v>174</v>
+      <c r="A163" s="9">
+        <v>901500</v>
+      </c>
+      <c r="B163" s="10" t="s">
+        <v>175</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="164" spans="1:4">
-      <c r="A164" s="9">
-        <v>209178</v>
-      </c>
-      <c r="B164" s="10" t="s">
-        <v>175</v>
+      <c r="A164" s="5">
+        <v>195814</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="C164" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="165" spans="1:4">
-      <c r="A165" s="6">
-        <v>211558</v>
+      <c r="A165" s="5">
+        <v>225674</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="5">
-        <v>217695</v>
+        <v>186664</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="5">
-        <v>205130</v>
+        <v>234426</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="168" spans="1:4">
-      <c r="A168" s="5">
-        <v>202379</v>
-      </c>
-      <c r="B168" s="6" t="s">
-        <v>179</v>
+      <c r="A168" s="9">
+        <v>209178</v>
+      </c>
+      <c r="B168" s="10" t="s">
+        <v>180</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="169" spans="1:4">
-      <c r="A169" s="5">
-        <v>905161</v>
+      <c r="A169" s="6">
+        <v>211558</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="5">
-        <v>903942</v>
+        <v>217695</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="5">
-        <v>208107</v>
+        <v>205130</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="172" spans="1:4">
-      <c r="A172" s="9">
-        <v>192993</v>
-      </c>
-      <c r="B172" s="10" t="s">
-        <v>183</v>
+      <c r="A172" s="5">
+        <v>202379</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="5">
-        <v>189186</v>
+        <v>905161</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="174" spans="1:4">
-      <c r="A174" s="9">
-        <v>904950</v>
-      </c>
-      <c r="B174" s="10" t="s">
-        <v>185</v>
+      <c r="A174" s="5">
+        <v>903942</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>186</v>
       </c>
       <c r="C174" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="5">
-        <v>188592</v>
+        <v>208107</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>187</v>
+        <v>132</v>
       </c>
     </row>
     <row r="176" spans="1:4">
-      <c r="A176" s="6">
-        <v>210767</v>
-      </c>
-      <c r="B176" s="6" t="s">
+      <c r="A176" s="9">
+        <v>192993</v>
+      </c>
+      <c r="B176" s="10" t="s">
         <v>188</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>187</v>
+        <v>132</v>
       </c>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="5">
-        <v>210155</v>
+        <v>189186</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>189</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>187</v>
+        <v>132</v>
       </c>
     </row>
     <row r="178" spans="1:4">
-      <c r="A178" s="5">
-        <v>901756</v>
-      </c>
-      <c r="B178" s="6" t="s">
+      <c r="A178" s="9">
+        <v>904950</v>
+      </c>
+      <c r="B178" s="10" t="s">
         <v>190</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>187</v>
+        <v>132</v>
       </c>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="5">
-        <v>901557</v>
+        <v>188592</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>191</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="6">
-        <v>210625</v>
+        <v>210767</v>
       </c>
       <c r="B180" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D180" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="C180" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D180" s="6" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="5">
-        <v>215073</v>
+        <v>210155</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C181" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="182" spans="1:4">
-      <c r="A182" s="8">
-        <v>184790</v>
-      </c>
-      <c r="B182" s="8" t="s">
-        <v>194</v>
+      <c r="A182" s="5">
+        <v>901756</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="5">
-        <v>219807</v>
+        <v>901557</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="184" spans="1:4">
-      <c r="A184" s="9">
-        <v>211588</v>
-      </c>
-      <c r="B184" s="10" t="s">
-        <v>196</v>
+      <c r="A184" s="6">
+        <v>210625</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="5">
-        <v>214908</v>
+        <v>215073</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="186" spans="1:4">
-      <c r="A186" s="5">
-        <v>211318</v>
-      </c>
-      <c r="B186" s="6" t="s">
-        <v>198</v>
+      <c r="A186" s="8">
+        <v>184790</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>199</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="5">
-        <v>210787</v>
+        <v>219807</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>200</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="9">
-        <v>210135</v>
+        <v>211588</v>
       </c>
       <c r="B188" s="10" t="s">
         <v>201</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="189" spans="1:4">
-      <c r="A189" s="9">
-        <v>210264</v>
-      </c>
-      <c r="B189" s="10" t="s">
+      <c r="A189" s="5">
+        <v>214908</v>
+      </c>
+      <c r="B189" s="6" t="s">
         <v>202</v>
       </c>
       <c r="C189" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="190" spans="1:4">
-      <c r="A190" s="9">
-        <v>218359</v>
-      </c>
-      <c r="B190" s="10" t="s">
+      <c r="A190" s="5">
+        <v>211318</v>
+      </c>
+      <c r="B190" s="6" t="s">
         <v>203</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="9">
-        <v>211594</v>
+        <v>182998</v>
       </c>
       <c r="B191" s="10" t="s">
         <v>204</v>
@@ -5242,12 +5298,12 @@
         <v>13</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="9">
-        <v>224562</v>
+        <v>217707</v>
       </c>
       <c r="B192" s="10" t="s">
         <v>205</v>
@@ -5256,12 +5312,12 @@
         <v>13</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="9">
-        <v>212815</v>
+        <v>189900</v>
       </c>
       <c r="B193" s="10" t="s">
         <v>206</v>
@@ -5270,26 +5326,26 @@
         <v>10</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="9">
-        <v>189900</v>
+        <v>211575</v>
       </c>
       <c r="B194" s="10" t="s">
         <v>207</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="9">
-        <v>217164</v>
+        <v>212815</v>
       </c>
       <c r="B195" s="10" t="s">
         <v>208</v>
@@ -5298,362 +5354,362 @@
         <v>10</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="9">
-        <v>212657</v>
+        <v>209640</v>
       </c>
       <c r="B196" s="10" t="s">
         <v>209</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="9">
-        <v>213366</v>
+        <v>218359</v>
       </c>
       <c r="B197" s="10" t="s">
         <v>210</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="198" spans="1:4">
-      <c r="A198" s="9">
-        <v>211575</v>
-      </c>
-      <c r="B198" s="10" t="s">
+      <c r="A198" s="5">
+        <v>210787</v>
+      </c>
+      <c r="B198" s="6" t="s">
         <v>211</v>
       </c>
       <c r="C198" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="9">
-        <v>211407</v>
+        <v>210135</v>
       </c>
       <c r="B199" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D199" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="C199" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D199" s="6" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="9">
-        <v>211410</v>
+        <v>210264</v>
       </c>
       <c r="B200" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C200" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="9">
-        <v>211264</v>
+        <v>211594</v>
       </c>
       <c r="B201" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C201" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="9">
-        <v>182998</v>
+        <v>224562</v>
       </c>
       <c r="B202" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C202" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="9">
-        <v>217707</v>
+        <v>217164</v>
       </c>
       <c r="B203" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="9">
-        <v>217693</v>
+        <v>212657</v>
       </c>
       <c r="B204" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="9">
-        <v>217703</v>
+        <v>213366</v>
       </c>
       <c r="B205" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C205" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="9">
-        <v>212877</v>
+        <v>211407</v>
       </c>
       <c r="B206" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="9">
+        <v>211410</v>
+      </c>
+      <c r="B207" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="C207" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D207" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4">
+      <c r="A208" s="9">
+        <v>211264</v>
+      </c>
+      <c r="B208" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="C208" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D208" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
+      <c r="A209" s="9">
+        <v>217693</v>
+      </c>
+      <c r="B209" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="C209" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D209" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
+      <c r="A210" s="9">
+        <v>217703</v>
+      </c>
+      <c r="B210" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C210" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D210" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
+      <c r="A211" s="9">
+        <v>212877</v>
+      </c>
+      <c r="B211" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="C211" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D211" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
+      <c r="A212" s="9">
         <v>905147</v>
       </c>
-      <c r="B207" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="C207" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D207" s="6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4">
-      <c r="A208" s="6">
+      <c r="B212" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="C212" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
+      <c r="A213" s="9">
+        <v>326411</v>
+      </c>
+      <c r="B213" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="C213" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D213" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
+      <c r="A214" s="6">
         <v>211937</v>
       </c>
-      <c r="B208" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C208" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D208" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4">
-      <c r="A209" s="5">
-        <v>240677</v>
-      </c>
-      <c r="B209" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="C209" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D209" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4">
-      <c r="A210" s="5">
-        <v>259806</v>
-      </c>
-      <c r="B210" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C210" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D210" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4">
-      <c r="A211" s="5">
-        <v>236217</v>
-      </c>
-      <c r="B211" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="C211" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D211" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4">
-      <c r="A212" s="5">
-        <v>248907</v>
-      </c>
-      <c r="B212" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="C212" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D212" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4">
-      <c r="A213" s="5">
-        <v>260944</v>
-      </c>
-      <c r="B213" s="6" t="s">
+      <c r="B214" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="C213" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D213" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4">
-      <c r="A214" s="5">
-        <v>257606</v>
-      </c>
-      <c r="B214" s="6" t="s">
+      <c r="C214" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D214" s="6" t="s">
         <v>229</v>
-      </c>
-      <c r="C214" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D214" s="6" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="5">
-        <v>251924</v>
+        <v>240677</v>
       </c>
       <c r="B215" s="6" t="s">
         <v>230</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="5">
-        <v>273299</v>
+        <v>259806</v>
       </c>
       <c r="B216" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C216" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D216" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="C216" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D216" s="6" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="5">
-        <v>247704</v>
+        <v>236217</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C217" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="5">
-        <v>230397</v>
+        <v>248907</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C218" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="5">
-        <v>263416</v>
+        <v>260944</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="5">
-        <v>248322</v>
+        <v>257606</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C220" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="5">
-        <v>248319</v>
+        <v>251924</v>
       </c>
       <c r="B221" s="6" t="s">
         <v>237</v>
@@ -5662,26 +5718,26 @@
         <v>5</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="5">
-        <v>258463</v>
+        <v>273299</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>238</v>
       </c>
       <c r="C222" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="5">
-        <v>261764</v>
+        <v>247704</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>239</v>
@@ -5690,68 +5746,68 @@
         <v>10</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="5">
-        <v>262062</v>
+        <v>230397</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>240</v>
       </c>
       <c r="C224" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="5">
-        <v>265806</v>
+        <v>263416</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>241</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="5">
-        <v>265801</v>
+        <v>259803</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>242</v>
       </c>
       <c r="C226" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="227" spans="1:4">
-      <c r="A227" s="9">
-        <v>210590</v>
-      </c>
-      <c r="B227" s="9" t="s">
+      <c r="A227" s="5">
+        <v>282153</v>
+      </c>
+      <c r="B227" s="6" t="s">
         <v>243</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="5">
-        <v>257603</v>
+        <v>262062</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>244</v>
@@ -5760,376 +5816,376 @@
         <v>13</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="5">
-        <v>253772</v>
+        <v>248322</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>245</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="5">
-        <v>259803</v>
+        <v>248319</v>
       </c>
       <c r="B230" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C230" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D230" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="C230" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D230" s="6" t="s">
-        <v>236</v>
-      </c>
     </row>
     <row r="231" spans="1:4">
-      <c r="A231" s="8">
-        <v>212982</v>
-      </c>
-      <c r="B231" s="8" t="s">
-        <v>247</v>
+      <c r="A231" s="5">
+        <v>258463</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>248</v>
       </c>
       <c r="C231" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="5">
-        <v>271938</v>
+        <v>261764</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C232" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="5">
-        <v>282153</v>
+        <v>265806</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="234" spans="1:4">
-      <c r="A234" s="9">
-        <v>257697</v>
-      </c>
-      <c r="B234" s="9" t="s">
-        <v>250</v>
+      <c r="A234" s="5">
+        <v>265801</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="C234" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="235" spans="1:4">
-      <c r="A235" s="5">
-        <v>265822</v>
-      </c>
-      <c r="B235" s="6" t="s">
-        <v>251</v>
+      <c r="A235" s="9">
+        <v>210590</v>
+      </c>
+      <c r="B235" s="9" t="s">
+        <v>252</v>
       </c>
       <c r="C235" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="5">
-        <v>266499</v>
+        <v>257603</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="5">
-        <v>253776</v>
+        <v>253772</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="238" spans="1:4">
-      <c r="A238" s="5">
-        <v>270795</v>
-      </c>
-      <c r="B238" s="6" t="s">
-        <v>254</v>
+      <c r="A238" s="8">
+        <v>212982</v>
+      </c>
+      <c r="B238" s="8" t="s">
+        <v>255</v>
       </c>
       <c r="C238" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="239" spans="1:4">
-      <c r="A239" s="8">
-        <v>276035</v>
-      </c>
-      <c r="B239" s="8" t="s">
-        <v>255</v>
+      <c r="A239" s="5">
+        <v>271938</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="C239" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="240" spans="1:4">
-      <c r="A240" s="6">
-        <v>285839</v>
-      </c>
-      <c r="B240" s="6" t="s">
-        <v>256</v>
+      <c r="A240" s="9">
+        <v>257697</v>
+      </c>
+      <c r="B240" s="9" t="s">
+        <v>257</v>
       </c>
       <c r="C240" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="241" spans="1:4">
-      <c r="A241" s="6">
-        <v>278078</v>
+      <c r="A241" s="5">
+        <v>265822</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C241" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="242" spans="1:4">
       <c r="A242" s="5">
-        <v>264179</v>
+        <v>266499</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C242" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="243" spans="1:4">
-      <c r="A243" s="6">
-        <v>281972</v>
+      <c r="A243" s="5">
+        <v>253776</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C243" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="244" spans="1:4">
       <c r="A244" s="5">
-        <v>276707</v>
+        <v>270795</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C244" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="245" spans="1:4">
-      <c r="A245" s="9">
-        <v>266464</v>
-      </c>
-      <c r="B245" s="9" t="s">
-        <v>261</v>
+      <c r="A245" s="8">
+        <v>276035</v>
+      </c>
+      <c r="B245" s="8" t="s">
+        <v>262</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="246" spans="1:4">
       <c r="A246" s="6">
-        <v>279453</v>
+        <v>285839</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C246" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="247" spans="1:4">
-      <c r="A247" s="9">
-        <v>273291</v>
-      </c>
-      <c r="B247" s="10" t="s">
-        <v>263</v>
+      <c r="A247" s="6">
+        <v>278078</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>264</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="5">
-        <v>279511</v>
+        <v>264179</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C248" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="249" spans="1:4">
-      <c r="A249" s="5">
-        <v>270784</v>
+      <c r="A249" s="6">
+        <v>281972</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C249" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="5">
-        <v>271943</v>
+        <v>276707</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>267</v>
       </c>
       <c r="C250" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="251" spans="1:4">
-      <c r="A251" s="5">
-        <v>247695</v>
-      </c>
-      <c r="B251" s="6" t="s">
+      <c r="A251" s="9">
+        <v>266464</v>
+      </c>
+      <c r="B251" s="9" t="s">
         <v>268</v>
       </c>
       <c r="C251" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="252" spans="1:4">
-      <c r="A252" s="5">
-        <v>253781</v>
+      <c r="A252" s="6">
+        <v>279453</v>
       </c>
       <c r="B252" s="6" t="s">
         <v>269</v>
       </c>
       <c r="C252" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="253" spans="1:4">
-      <c r="A253" s="5">
-        <v>211631</v>
-      </c>
-      <c r="B253" s="6" t="s">
+      <c r="A253" s="9">
+        <v>273291</v>
+      </c>
+      <c r="B253" s="10" t="s">
         <v>270</v>
       </c>
       <c r="C253" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="254" spans="1:4">
-      <c r="A254" s="6">
-        <v>278079</v>
+      <c r="A254" s="5">
+        <v>279511</v>
       </c>
       <c r="B254" s="6" t="s">
         <v>271</v>
       </c>
       <c r="C254" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="255" spans="1:4">
-      <c r="A255" s="5">
-        <v>273293</v>
+      <c r="A255" s="6">
+        <v>277539</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>272</v>
@@ -6138,12 +6194,12 @@
         <v>13</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="256" spans="1:4">
-      <c r="A256" s="5">
-        <v>269965</v>
+      <c r="A256" s="6">
+        <v>278647</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>273</v>
@@ -6152,54 +6208,54 @@
         <v>8</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="257" spans="1:4">
       <c r="A257" s="5">
-        <v>258464</v>
+        <v>279512</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>274</v>
       </c>
       <c r="C257" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D257" s="6" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="5">
-        <v>259796</v>
+        <v>258455</v>
       </c>
       <c r="B258" s="6" t="s">
         <v>275</v>
       </c>
       <c r="C258" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D258" s="6" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="259" spans="1:4">
       <c r="A259" s="6">
-        <v>276388</v>
+        <v>284046</v>
       </c>
       <c r="B259" s="6" t="s">
         <v>276</v>
       </c>
       <c r="C259" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D259" s="6" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="5">
-        <v>258455</v>
+        <v>271943</v>
       </c>
       <c r="B260" s="6" t="s">
         <v>277</v>
@@ -6208,572 +6264,572 @@
         <v>10</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
     </row>
     <row r="261" spans="1:4">
       <c r="A261" s="5">
-        <v>246412</v>
+        <v>270784</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>278</v>
       </c>
       <c r="C261" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="262" spans="1:4">
-      <c r="A262" s="6">
-        <v>278647</v>
+      <c r="A262" s="5">
+        <v>247695</v>
       </c>
       <c r="B262" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C262" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D262" s="6" t="s">
         <v>279</v>
-      </c>
-      <c r="C262" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D262" s="6" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="5">
-        <v>265803</v>
+        <v>253781</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C263" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="5">
-        <v>259798</v>
+        <v>211631</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C264" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D264" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="265" spans="1:4">
-      <c r="A265" s="5">
-        <v>261757</v>
+      <c r="A265" s="6">
+        <v>278079</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C265" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="266" spans="1:4">
-      <c r="A266" s="9">
-        <v>257611</v>
-      </c>
-      <c r="B266" s="9" t="s">
-        <v>283</v>
+      <c r="A266" s="5">
+        <v>273293</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>284</v>
       </c>
       <c r="C266" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="267" spans="1:4">
       <c r="A267" s="5">
-        <v>279512</v>
+        <v>269965</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C267" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="268" spans="1:4">
-      <c r="A268" s="6">
-        <v>273152</v>
+      <c r="A268" s="5">
+        <v>258464</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C268" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="269" spans="1:4">
-      <c r="A269" s="6">
-        <v>284046</v>
+      <c r="A269" s="5">
+        <v>259796</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C269" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D269" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="270" spans="1:4">
-      <c r="A270" s="8">
-        <v>236219</v>
-      </c>
-      <c r="B270" s="8" t="s">
-        <v>287</v>
+      <c r="A270" s="6">
+        <v>276388</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>288</v>
       </c>
       <c r="C270" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D270" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="271" spans="1:4">
-      <c r="A271" s="6">
-        <v>277539</v>
+      <c r="A271" s="5">
+        <v>246412</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C271" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="5">
-        <v>262054</v>
+        <v>265803</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C272" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D272" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="5">
-        <v>274982</v>
+        <v>259798</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C273" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D273" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="274" spans="1:4">
-      <c r="A274" s="6">
-        <v>273421</v>
+      <c r="A274" s="5">
+        <v>261757</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C274" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D274" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="9">
-        <v>271948</v>
-      </c>
-      <c r="B275" s="10" t="s">
-        <v>292</v>
+        <v>257611</v>
+      </c>
+      <c r="B275" s="9" t="s">
+        <v>293</v>
       </c>
       <c r="C275" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="276" spans="1:4">
-      <c r="A276" s="5">
-        <v>280959</v>
+      <c r="A276" s="6">
+        <v>273152</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C276" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D276" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="277" spans="1:4">
-      <c r="A277" s="6">
-        <v>278680</v>
-      </c>
-      <c r="B277" s="6" t="s">
-        <v>294</v>
+      <c r="A277" s="8">
+        <v>236219</v>
+      </c>
+      <c r="B277" s="8" t="s">
+        <v>295</v>
       </c>
       <c r="C277" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D277" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="278" spans="1:4">
-      <c r="A278" s="6">
-        <v>283735</v>
+      <c r="A278" s="5">
+        <v>262054</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C278" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D278" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="279" spans="1:4">
-      <c r="A279" s="6">
-        <v>261777</v>
+      <c r="A279" s="5">
+        <v>274982</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C279" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D279" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="280" spans="1:4">
       <c r="A280" s="6">
-        <v>280875</v>
+        <v>273421</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C280" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D280" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="281" spans="1:4">
       <c r="A281" s="9">
-        <v>279540</v>
-      </c>
-      <c r="B281" s="9" t="s">
-        <v>298</v>
+        <v>271948</v>
+      </c>
+      <c r="B281" s="10" t="s">
+        <v>299</v>
       </c>
       <c r="C281" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D281" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="282" spans="1:4">
-      <c r="A282" s="6">
-        <v>271879</v>
+      <c r="A282" s="5">
+        <v>280959</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C282" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="283" spans="1:4">
-      <c r="A283" s="5">
-        <v>249564</v>
+      <c r="A283" s="6">
+        <v>278680</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C283" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D283" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="284" spans="1:4">
       <c r="A284" s="6">
-        <v>215555</v>
+        <v>283735</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C284" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D284" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="285" spans="1:4">
       <c r="A285" s="6">
-        <v>280880</v>
+        <v>261777</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C285" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D285" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="286" spans="1:4">
       <c r="A286" s="6">
-        <v>236145</v>
+        <v>280875</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C286" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="287" spans="1:4">
-      <c r="A287" s="8">
-        <v>274985</v>
-      </c>
-      <c r="B287" s="8" t="s">
-        <v>304</v>
+      <c r="A287" s="9">
+        <v>279540</v>
+      </c>
+      <c r="B287" s="9" t="s">
+        <v>305</v>
       </c>
       <c r="C287" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D287" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="288" spans="1:4">
-      <c r="A288" s="9">
-        <v>279543</v>
-      </c>
-      <c r="B288" s="9" t="s">
-        <v>305</v>
+      <c r="A288" s="6">
+        <v>271879</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>306</v>
       </c>
       <c r="C288" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D288" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="289" spans="1:4">
       <c r="A289" s="5">
-        <v>270788</v>
+        <v>249564</v>
       </c>
       <c r="B289" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C289" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D289" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="290" spans="1:4">
       <c r="A290" s="6">
-        <v>285783</v>
+        <v>215555</v>
       </c>
       <c r="B290" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C290" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="291" spans="1:4">
-      <c r="A291" s="8">
-        <v>275099</v>
-      </c>
-      <c r="B291" s="8" t="s">
-        <v>308</v>
+      <c r="A291" s="6">
+        <v>280880</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>309</v>
       </c>
       <c r="C291" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D291" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="292" spans="1:4">
-      <c r="A292" s="9">
-        <v>273295</v>
-      </c>
-      <c r="B292" s="10" t="s">
-        <v>309</v>
+      <c r="A292" s="6">
+        <v>236145</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>310</v>
       </c>
       <c r="C292" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D292" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="293" spans="1:4">
-      <c r="A293" s="6">
-        <v>276385</v>
-      </c>
-      <c r="B293" s="6" t="s">
-        <v>310</v>
+      <c r="A293" s="8">
+        <v>274985</v>
+      </c>
+      <c r="B293" s="8" t="s">
+        <v>311</v>
       </c>
       <c r="C293" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D293" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="294" spans="1:4">
       <c r="A294" s="9">
-        <v>282669</v>
+        <v>279543</v>
       </c>
       <c r="B294" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C294" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D294" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="295" spans="1:4">
       <c r="A295" s="5">
-        <v>280956</v>
+        <v>270788</v>
       </c>
       <c r="B295" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C295" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
     </row>
     <row r="296" spans="1:4">
-      <c r="A296" s="5">
-        <v>213858</v>
+      <c r="A296" s="6">
+        <v>285783</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C296" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D296" s="6" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="297" spans="1:4">
-      <c r="A297" s="5">
-        <v>268097</v>
-      </c>
-      <c r="B297" s="6" t="s">
+      <c r="A297" s="8">
+        <v>275099</v>
+      </c>
+      <c r="B297" s="8" t="s">
         <v>315</v>
       </c>
       <c r="C297" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="298" spans="1:4">
-      <c r="A298" s="6">
-        <v>281970</v>
-      </c>
-      <c r="B298" s="6" t="s">
+      <c r="A298" s="9">
+        <v>273295</v>
+      </c>
+      <c r="B298" s="10" t="s">
         <v>316</v>
       </c>
       <c r="C298" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D298" s="6" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="299" spans="1:4">
-      <c r="A299" s="5">
-        <v>263409</v>
+      <c r="A299" s="6">
+        <v>276385</v>
       </c>
       <c r="B299" s="6" t="s">
         <v>317</v>
       </c>
       <c r="C299" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="300" spans="1:4">
-      <c r="A300" s="6">
-        <v>210531</v>
-      </c>
-      <c r="B300" s="6" t="s">
+      <c r="A300" s="9">
+        <v>282669</v>
+      </c>
+      <c r="B300" s="9" t="s">
         <v>318</v>
       </c>
       <c r="C300" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D300" s="6" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="301" spans="1:4">
-      <c r="A301" s="6">
-        <v>276019</v>
+      <c r="A301" s="5">
+        <v>280956</v>
       </c>
       <c r="B301" s="6" t="s">
         <v>319</v>
@@ -6782,21 +6838,21 @@
         <v>13</v>
       </c>
       <c r="D301" s="6" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="302" spans="1:4">
-      <c r="A302" s="9">
-        <v>272827</v>
-      </c>
-      <c r="B302" s="9" t="s">
+      <c r="A302" s="8">
+        <v>282654</v>
+      </c>
+      <c r="B302" s="8" t="s">
         <v>320</v>
       </c>
       <c r="C302" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D302" s="6" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -6810,63 +6866,63 @@
         <v>8</v>
       </c>
       <c r="D303" s="6" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="304" spans="1:4">
       <c r="A304" s="5">
-        <v>246465</v>
+        <v>263409</v>
       </c>
       <c r="B304" s="6" t="s">
         <v>322</v>
       </c>
       <c r="C304" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D304" s="6" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="305" spans="1:4">
-      <c r="A305" s="6">
-        <v>261778</v>
-      </c>
-      <c r="B305" s="6" t="s">
+      <c r="A305" s="9">
+        <v>284122</v>
+      </c>
+      <c r="B305" s="9" t="s">
         <v>323</v>
       </c>
       <c r="C305" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D305" s="6" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="306" spans="1:4">
-      <c r="A306" s="5">
-        <v>289953</v>
-      </c>
-      <c r="B306" s="6" t="s">
+      <c r="A306" s="9">
+        <v>278087</v>
+      </c>
+      <c r="B306" s="9" t="s">
         <v>324</v>
       </c>
       <c r="C306" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D306" s="6" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="307" spans="1:4">
-      <c r="A307" s="9">
-        <v>284122</v>
-      </c>
-      <c r="B307" s="9" t="s">
+      <c r="A307" s="5">
+        <v>283749</v>
+      </c>
+      <c r="B307" s="6" t="s">
         <v>325</v>
       </c>
       <c r="C307" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D307" s="6" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -6880,684 +6936,684 @@
         <v>10</v>
       </c>
       <c r="D308" s="6" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="309" spans="1:4">
-      <c r="A309" s="8">
-        <v>282654</v>
-      </c>
-      <c r="B309" s="8" t="s">
+      <c r="A309" s="5">
+        <v>283601</v>
+      </c>
+      <c r="B309" s="6" t="s">
         <v>327</v>
       </c>
       <c r="C309" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D309" s="6" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="310" spans="1:4">
       <c r="A310" s="9">
-        <v>282149</v>
+        <v>285896</v>
       </c>
       <c r="B310" s="9" t="s">
         <v>328</v>
       </c>
       <c r="C310" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D310" s="6" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
     </row>
     <row r="311" spans="1:4">
       <c r="A311" s="5">
-        <v>291328</v>
+        <v>213858</v>
       </c>
       <c r="B311" s="6" t="s">
         <v>329</v>
       </c>
       <c r="C311" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D311" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="312" spans="1:4">
-      <c r="A312" s="9">
-        <v>275109</v>
-      </c>
-      <c r="B312" s="9" t="s">
+      <c r="A312" s="5">
+        <v>268097</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="C312" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D312" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="C312" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D312" s="6" t="s">
-        <v>314</v>
-      </c>
     </row>
     <row r="313" spans="1:4">
-      <c r="A313" s="5">
-        <v>284048</v>
+      <c r="A313" s="6">
+        <v>281970</v>
       </c>
       <c r="B313" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C313" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D313" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="314" spans="1:4">
-      <c r="A314" s="5">
-        <v>288733</v>
+      <c r="A314" s="6">
+        <v>210531</v>
       </c>
       <c r="B314" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C314" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D314" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="315" spans="1:4">
-      <c r="A315" s="5">
-        <v>211367</v>
+      <c r="A315" s="6">
+        <v>276019</v>
       </c>
       <c r="B315" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C315" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D315" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="316" spans="1:4">
-      <c r="A316" s="5">
-        <v>265617</v>
-      </c>
-      <c r="B316" s="6" t="s">
-        <v>334</v>
+      <c r="A316" s="9">
+        <v>272827</v>
+      </c>
+      <c r="B316" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="C316" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D316" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="317" spans="1:4">
-      <c r="A317" s="9">
-        <v>278087</v>
-      </c>
-      <c r="B317" s="9" t="s">
-        <v>335</v>
+      <c r="A317" s="5">
+        <v>246465</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>336</v>
       </c>
       <c r="C317" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D317" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="318" spans="1:4">
-      <c r="A318" s="9">
-        <v>283807</v>
-      </c>
-      <c r="B318" s="10" t="s">
-        <v>336</v>
+      <c r="A318" s="6">
+        <v>261778</v>
+      </c>
+      <c r="B318" s="6" t="s">
+        <v>337</v>
       </c>
       <c r="C318" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D318" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="319" spans="1:4">
       <c r="A319" s="5">
-        <v>283601</v>
+        <v>289953</v>
       </c>
       <c r="B319" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C319" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D319" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="320" spans="1:4">
       <c r="A320" s="9">
-        <v>290978</v>
+        <v>282149</v>
       </c>
       <c r="B320" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C320" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D320" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="321" spans="1:4">
-      <c r="A321" s="6">
-        <v>272821</v>
+      <c r="A321" s="5">
+        <v>291328</v>
       </c>
       <c r="B321" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C321" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D321" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="322" spans="1:4">
       <c r="A322" s="9">
-        <v>285277</v>
+        <v>275109</v>
       </c>
       <c r="B322" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C322" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D322" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="323" spans="1:4">
       <c r="A323" s="5">
-        <v>284923</v>
+        <v>284048</v>
       </c>
       <c r="B323" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C323" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D323" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="324" spans="1:4">
-      <c r="A324" s="8">
-        <v>275104</v>
-      </c>
-      <c r="B324" s="8" t="s">
-        <v>342</v>
+      <c r="A324" s="5">
+        <v>288733</v>
+      </c>
+      <c r="B324" s="6" t="s">
+        <v>343</v>
       </c>
       <c r="C324" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D324" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" s="5">
-        <v>275006</v>
+        <v>211367</v>
       </c>
       <c r="B325" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C325" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D325" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="326" spans="1:4">
-      <c r="A326" s="9">
-        <v>294186</v>
-      </c>
-      <c r="B326" s="10" t="s">
-        <v>344</v>
+      <c r="A326" s="5">
+        <v>265617</v>
+      </c>
+      <c r="B326" s="6" t="s">
+        <v>345</v>
       </c>
       <c r="C326" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D326" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="327" spans="1:4">
-      <c r="A327" s="5">
-        <v>266461</v>
-      </c>
-      <c r="B327" s="6" t="s">
-        <v>345</v>
+      <c r="A327" s="9">
+        <v>283807</v>
+      </c>
+      <c r="B327" s="10" t="s">
+        <v>346</v>
       </c>
       <c r="C327" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D327" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="328" spans="1:4">
       <c r="A328" s="9">
-        <v>298237</v>
-      </c>
-      <c r="B328" s="10" t="s">
-        <v>346</v>
+        <v>290978</v>
+      </c>
+      <c r="B328" s="9" t="s">
+        <v>347</v>
       </c>
       <c r="C328" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D328" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="329" spans="1:4">
-      <c r="A329" s="5">
-        <v>275021</v>
+      <c r="A329" s="6">
+        <v>272821</v>
       </c>
       <c r="B329" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C329" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D329" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="330" spans="1:4">
-      <c r="A330" s="5">
-        <v>283749</v>
-      </c>
-      <c r="B330" s="6" t="s">
-        <v>348</v>
+      <c r="A330" s="9">
+        <v>285277</v>
+      </c>
+      <c r="B330" s="9" t="s">
+        <v>349</v>
       </c>
       <c r="C330" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D330" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="331" spans="1:4">
-      <c r="A331" s="9">
-        <v>285896</v>
-      </c>
-      <c r="B331" s="9" t="s">
-        <v>349</v>
+      <c r="A331" s="5">
+        <v>284923</v>
+      </c>
+      <c r="B331" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="C331" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D331" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="332" spans="1:4">
-      <c r="A332" s="6">
-        <v>217602</v>
-      </c>
-      <c r="B332" s="6" t="s">
-        <v>350</v>
+      <c r="A332" s="8">
+        <v>275104</v>
+      </c>
+      <c r="B332" s="8" t="s">
+        <v>351</v>
       </c>
       <c r="C332" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D332" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="333" spans="1:4">
       <c r="A333" s="5">
-        <v>276056</v>
+        <v>275006</v>
       </c>
       <c r="B333" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C333" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D333" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="334" spans="1:4">
-      <c r="A334" s="8">
-        <v>289669</v>
-      </c>
-      <c r="B334" s="8" t="s">
-        <v>352</v>
+      <c r="A334" s="9">
+        <v>294186</v>
+      </c>
+      <c r="B334" s="10" t="s">
+        <v>353</v>
       </c>
       <c r="C334" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D334" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" s="5">
-        <v>286123</v>
+        <v>266461</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C335" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D335" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="336" spans="1:4">
       <c r="A336" s="9">
-        <v>294185</v>
+        <v>298237</v>
       </c>
       <c r="B336" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C336" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D336" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="337" spans="1:4">
-      <c r="A337" s="9">
-        <v>273305</v>
-      </c>
-      <c r="B337" s="10" t="s">
-        <v>355</v>
+      <c r="A337" s="5">
+        <v>275021</v>
+      </c>
+      <c r="B337" s="6" t="s">
+        <v>356</v>
       </c>
       <c r="C337" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D337" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="338" spans="1:4">
-      <c r="A338" s="5">
-        <v>284332</v>
+      <c r="A338" s="6">
+        <v>217602</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C338" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D338" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="339" spans="1:4">
-      <c r="A339" s="9">
-        <v>281004</v>
-      </c>
-      <c r="B339" s="10" t="s">
-        <v>357</v>
+      <c r="A339" s="5">
+        <v>276056</v>
+      </c>
+      <c r="B339" s="6" t="s">
+        <v>358</v>
       </c>
       <c r="C339" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D339" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="340" spans="1:4">
-      <c r="A340" s="9">
-        <v>271929</v>
-      </c>
-      <c r="B340" s="10" t="s">
-        <v>358</v>
+      <c r="A340" s="8">
+        <v>289669</v>
+      </c>
+      <c r="B340" s="8" t="s">
+        <v>359</v>
       </c>
       <c r="C340" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D340" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="341" spans="1:4">
       <c r="A341" s="5">
-        <v>284330</v>
+        <v>286123</v>
       </c>
       <c r="B341" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C341" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D341" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="342" spans="1:4">
-      <c r="A342" s="8">
-        <v>288902</v>
-      </c>
-      <c r="B342" s="8" t="s">
-        <v>360</v>
+      <c r="A342" s="9">
+        <v>294185</v>
+      </c>
+      <c r="B342" s="10" t="s">
+        <v>361</v>
       </c>
       <c r="C342" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D342" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="343" spans="1:4">
       <c r="A343" s="9">
-        <v>278746</v>
+        <v>273305</v>
       </c>
       <c r="B343" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C343" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D343" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="344" spans="1:4">
-      <c r="A344" s="9">
-        <v>283833</v>
-      </c>
-      <c r="B344" s="10" t="s">
-        <v>362</v>
+      <c r="A344" s="5">
+        <v>284332</v>
+      </c>
+      <c r="B344" s="6" t="s">
+        <v>363</v>
       </c>
       <c r="C344" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D344" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="345" spans="1:4">
       <c r="A345" s="9">
-        <v>292765</v>
+        <v>281004</v>
       </c>
       <c r="B345" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C345" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D345" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="346" spans="1:4">
       <c r="A346" s="9">
-        <v>294086</v>
+        <v>271929</v>
       </c>
       <c r="B346" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C346" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D346" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="347" spans="1:4">
-      <c r="A347" s="9">
-        <v>280950</v>
-      </c>
-      <c r="B347" s="10" t="s">
-        <v>365</v>
+      <c r="A347" s="5">
+        <v>284330</v>
+      </c>
+      <c r="B347" s="6" t="s">
+        <v>366</v>
       </c>
       <c r="C347" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D347" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="348" spans="1:4">
-      <c r="A348" s="9">
-        <v>273284</v>
-      </c>
-      <c r="B348" s="10" t="s">
-        <v>366</v>
+      <c r="A348" s="8">
+        <v>288902</v>
+      </c>
+      <c r="B348" s="8" t="s">
+        <v>367</v>
       </c>
       <c r="C348" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D348" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="349" spans="1:4">
       <c r="A349" s="9">
-        <v>297287</v>
+        <v>278746</v>
       </c>
       <c r="B349" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C349" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D349" s="6" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="350" spans="1:4">
-      <c r="A350" s="5">
-        <v>284331</v>
-      </c>
-      <c r="B350" s="6" t="s">
-        <v>368</v>
+      <c r="A350" s="9">
+        <v>283833</v>
+      </c>
+      <c r="B350" s="10" t="s">
+        <v>369</v>
       </c>
       <c r="C350" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D350" s="6" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
     </row>
     <row r="351" spans="1:4">
-      <c r="A351" s="5">
-        <v>291033</v>
-      </c>
-      <c r="B351" s="6" t="s">
+      <c r="A351" s="9">
+        <v>292765</v>
+      </c>
+      <c r="B351" s="10" t="s">
         <v>370</v>
       </c>
       <c r="C351" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D351" s="6" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
     </row>
     <row r="352" spans="1:4">
       <c r="A352" s="9">
-        <v>278747</v>
+        <v>294086</v>
       </c>
       <c r="B352" s="10" t="s">
         <v>371</v>
       </c>
       <c r="C352" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D352" s="6" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
     </row>
     <row r="353" spans="1:4">
       <c r="A353" s="9">
-        <v>263420</v>
+        <v>280950</v>
       </c>
       <c r="B353" s="10" t="s">
         <v>372</v>
       </c>
       <c r="C353" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D353" s="6" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
     </row>
     <row r="354" spans="1:4">
       <c r="A354" s="9">
-        <v>280074</v>
+        <v>273284</v>
       </c>
       <c r="B354" s="10" t="s">
         <v>373</v>
       </c>
       <c r="C354" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D354" s="6" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
     </row>
     <row r="355" spans="1:4">
       <c r="A355" s="9">
-        <v>284201</v>
+        <v>297287</v>
       </c>
       <c r="B355" s="10" t="s">
         <v>374</v>
       </c>
       <c r="C355" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D355" s="6" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
     </row>
     <row r="356" spans="1:4">
       <c r="A356" s="9">
-        <v>276712</v>
+        <v>280145</v>
       </c>
       <c r="B356" s="10" t="s">
         <v>375</v>
       </c>
       <c r="C356" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D356" s="6" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
     </row>
     <row r="357" spans="1:4">
       <c r="A357" s="9">
-        <v>280145</v>
+        <v>297292</v>
       </c>
       <c r="B357" s="10" t="s">
         <v>376</v>
@@ -7566,698 +7622,698 @@
         <v>10</v>
       </c>
       <c r="D357" s="6" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
     </row>
     <row r="358" spans="1:4">
-      <c r="A358" s="9">
-        <v>294947</v>
-      </c>
-      <c r="B358" s="10" t="s">
+      <c r="A358" s="5">
+        <v>284331</v>
+      </c>
+      <c r="B358" s="6" t="s">
         <v>377</v>
       </c>
       <c r="C358" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D358" s="6" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
     </row>
     <row r="359" spans="1:4">
-      <c r="A359" s="9">
-        <v>282686</v>
-      </c>
-      <c r="B359" s="10" t="s">
+      <c r="A359" s="5">
+        <v>291033</v>
+      </c>
+      <c r="B359" s="6" t="s">
         <v>378</v>
       </c>
       <c r="C359" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D359" s="6" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
     </row>
     <row r="360" spans="1:4">
       <c r="A360" s="9">
-        <v>282119</v>
+        <v>298124</v>
       </c>
       <c r="B360" s="10" t="s">
         <v>379</v>
       </c>
       <c r="C360" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D360" s="6" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
     </row>
     <row r="361" spans="1:4">
       <c r="A361" s="9">
-        <v>298124</v>
+        <v>298146</v>
       </c>
       <c r="B361" s="10" t="s">
         <v>380</v>
       </c>
       <c r="C361" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D361" s="6" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
     </row>
     <row r="362" spans="1:4">
       <c r="A362" s="9">
-        <v>297292</v>
+        <v>282119</v>
       </c>
       <c r="B362" s="10" t="s">
         <v>381</v>
       </c>
       <c r="C362" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D362" s="6" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
     </row>
     <row r="363" spans="1:4">
       <c r="A363" s="9">
-        <v>294511</v>
+        <v>282686</v>
       </c>
       <c r="B363" s="10" t="s">
         <v>382</v>
       </c>
       <c r="C363" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D363" s="6" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
     </row>
     <row r="364" spans="1:4">
       <c r="A364" s="9">
-        <v>298146</v>
+        <v>294511</v>
       </c>
       <c r="B364" s="10" t="s">
         <v>383</v>
       </c>
       <c r="C364" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D364" s="6" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
     </row>
     <row r="365" spans="1:4">
       <c r="A365" s="9">
-        <v>306811</v>
+        <v>278747</v>
       </c>
       <c r="B365" s="10" t="s">
         <v>384</v>
       </c>
       <c r="C365" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D365" s="6" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
     </row>
     <row r="366" spans="1:4">
       <c r="A366" s="9">
-        <v>298838</v>
+        <v>263420</v>
       </c>
       <c r="B366" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="C366" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D366" s="6" t="s">
         <v>385</v>
-      </c>
-      <c r="C366" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D366" s="6" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="367" spans="1:4">
       <c r="A367" s="9">
-        <v>302687</v>
+        <v>280074</v>
       </c>
       <c r="B367" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C367" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D367" s="6" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
     </row>
     <row r="368" spans="1:4">
       <c r="A368" s="9">
-        <v>249569</v>
+        <v>284201</v>
       </c>
       <c r="B368" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C368" s="7" t="s">
         <v>5</v>
       </c>
       <c r="D368" s="6" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
     </row>
     <row r="369" spans="1:4">
       <c r="A369" s="9">
-        <v>268080</v>
+        <v>276712</v>
       </c>
       <c r="B369" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C369" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D369" s="6" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
     </row>
     <row r="370" spans="1:4">
       <c r="A370" s="9">
-        <v>906064</v>
+        <v>294947</v>
       </c>
       <c r="B370" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C370" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D370" s="6" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
     </row>
     <row r="371" spans="1:4">
       <c r="A371" s="9">
-        <v>283744</v>
+        <v>306811</v>
       </c>
       <c r="B371" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C371" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D371" s="6" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
     </row>
     <row r="372" spans="1:4">
       <c r="A372" s="9">
-        <v>286107</v>
+        <v>298838</v>
       </c>
       <c r="B372" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C372" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D372" s="6" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
     </row>
     <row r="373" spans="1:4">
       <c r="A373" s="9">
-        <v>288732</v>
+        <v>302687</v>
       </c>
       <c r="B373" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C373" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D373" s="6" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
     </row>
     <row r="374" spans="1:4">
       <c r="A374" s="9">
-        <v>289565</v>
+        <v>249569</v>
       </c>
       <c r="B374" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C374" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D374" s="6" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
     </row>
     <row r="375" spans="1:4">
       <c r="A375" s="9">
-        <v>294936</v>
+        <v>268080</v>
       </c>
       <c r="B375" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C375" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D375" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="376" spans="1:4">
       <c r="A376" s="9">
-        <v>282016</v>
+        <v>906064</v>
       </c>
       <c r="B376" s="10" t="s">
         <v>396</v>
       </c>
       <c r="C376" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D376" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="377" spans="1:4">
       <c r="A377" s="9">
-        <v>298179</v>
+        <v>283744</v>
       </c>
       <c r="B377" s="10" t="s">
         <v>397</v>
       </c>
       <c r="C377" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D377" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="378" spans="1:4">
       <c r="A378" s="9">
-        <v>302250</v>
+        <v>286107</v>
       </c>
       <c r="B378" s="10" t="s">
         <v>398</v>
       </c>
       <c r="C378" s="7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D378" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="379" spans="1:4">
       <c r="A379" s="9">
-        <v>302251</v>
+        <v>288732</v>
       </c>
       <c r="B379" s="10" t="s">
         <v>399</v>
       </c>
       <c r="C379" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D379" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="380" spans="1:4">
       <c r="A380" s="9">
-        <v>302252</v>
+        <v>289565</v>
       </c>
       <c r="B380" s="10" t="s">
         <v>400</v>
       </c>
       <c r="C380" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D380" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="381" spans="1:4">
       <c r="A381" s="9">
-        <v>303944</v>
+        <v>284925</v>
       </c>
       <c r="B381" s="10" t="s">
         <v>401</v>
       </c>
       <c r="C381" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D381" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="382" spans="1:4">
       <c r="A382" s="9">
-        <v>302249</v>
+        <v>290948</v>
       </c>
       <c r="B382" s="10" t="s">
         <v>402</v>
       </c>
       <c r="C382" s="7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D382" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="383" spans="1:4">
       <c r="A383" s="9">
-        <v>326411</v>
+        <v>291329</v>
       </c>
       <c r="B383" s="10" t="s">
         <v>403</v>
       </c>
       <c r="C383" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D383" s="6" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
     </row>
     <row r="384" spans="1:4">
       <c r="A384" s="9">
-        <v>284925</v>
+        <v>281973</v>
       </c>
       <c r="B384" s="10" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C384" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D384" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="385" spans="1:4">
       <c r="A385" s="9">
-        <v>290948</v>
+        <v>275017</v>
       </c>
       <c r="B385" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C385" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D385" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="386" spans="1:4">
       <c r="A386" s="9">
-        <v>291329</v>
+        <v>294936</v>
       </c>
       <c r="B386" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C386" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D386" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="387" spans="1:4">
       <c r="A387" s="9">
-        <v>281973</v>
+        <v>282016</v>
       </c>
       <c r="B387" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C387" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D387" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="388" spans="1:4">
       <c r="A388" s="9">
-        <v>275017</v>
+        <v>298179</v>
       </c>
       <c r="B388" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="C388" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D388" s="6" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4">
+      <c r="A389" s="9">
+        <v>302250</v>
+      </c>
+      <c r="B389" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="C388" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D388" s="6" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="389" spans="1:4">
-      <c r="A389" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="B389" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="C389" s="8" t="s">
-        <v>5</v>
+      <c r="C389" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="D389" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="390" spans="1:4">
       <c r="A390" s="9">
-        <v>308642</v>
+        <v>302251</v>
       </c>
       <c r="B390" s="10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C390" s="7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D390" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="391" spans="1:4">
       <c r="A391" s="9">
-        <v>249878</v>
+        <v>302252</v>
       </c>
       <c r="B391" s="10" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C391" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D391" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="392" spans="1:4">
       <c r="A392" s="9">
-        <v>292239</v>
+        <v>303944</v>
       </c>
       <c r="B392" s="10" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C392" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D392" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="393" spans="1:4">
       <c r="A393" s="9">
-        <v>294618</v>
+        <v>302249</v>
       </c>
       <c r="B393" s="10" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C393" s="7" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D393" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="394" spans="1:4">
       <c r="A394" s="9">
-        <v>294620</v>
+        <v>228868</v>
       </c>
       <c r="B394" s="10" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C394" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D394" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="395" spans="1:4">
       <c r="A395" s="9">
-        <v>302685</v>
+        <v>283746</v>
       </c>
       <c r="B395" s="10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C395" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D395" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="396" spans="1:4">
       <c r="A396" s="9">
-        <v>207160</v>
+        <v>289949</v>
       </c>
       <c r="B396" s="10" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C396" s="7" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D396" s="6" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
     </row>
     <row r="397" spans="1:4">
       <c r="A397" s="9">
-        <v>181642</v>
+        <v>289564</v>
       </c>
       <c r="B397" s="10" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C397" s="7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D397" s="6" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
     </row>
     <row r="398" spans="1:4">
       <c r="A398" s="9">
-        <v>181737</v>
+        <v>294884</v>
       </c>
       <c r="B398" s="10" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C398" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D398" s="6" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
     </row>
     <row r="399" spans="1:4">
       <c r="A399" s="9">
-        <v>205160</v>
-      </c>
-      <c r="B399" s="10" t="s">
-        <v>421</v>
+        <v>249878</v>
+      </c>
+      <c r="B399" s="11" t="s">
+        <v>419</v>
       </c>
       <c r="C399" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D399" s="6" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
     </row>
     <row r="400" spans="1:4">
       <c r="A400" s="9">
-        <v>212794</v>
-      </c>
-      <c r="B400" s="10" t="s">
-        <v>422</v>
+        <v>292239</v>
+      </c>
+      <c r="B400" s="11" t="s">
+        <v>421</v>
       </c>
       <c r="C400" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D400" s="6" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
     </row>
     <row r="401" spans="1:4">
       <c r="A401" s="9">
-        <v>209640</v>
-      </c>
-      <c r="B401" s="10" t="s">
-        <v>423</v>
+        <v>294618</v>
+      </c>
+      <c r="B401" s="11" t="s">
+        <v>422</v>
       </c>
       <c r="C401" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D401" s="6" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
     </row>
     <row r="402" spans="1:4">
       <c r="A402" s="9">
-        <v>302253</v>
-      </c>
-      <c r="B402" s="10" t="s">
-        <v>424</v>
+        <v>294620</v>
+      </c>
+      <c r="B402" s="11" t="s">
+        <v>423</v>
       </c>
       <c r="C402" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D402" s="6" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
     </row>
     <row r="403" spans="1:4">
       <c r="A403" s="9">
-        <v>304230</v>
-      </c>
-      <c r="B403" s="10" t="s">
-        <v>425</v>
+        <v>302685</v>
+      </c>
+      <c r="B403" s="11" t="s">
+        <v>424</v>
       </c>
       <c r="C403" s="7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D403" s="6" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
     </row>
     <row r="404" spans="1:4">
       <c r="A404" s="9">
-        <v>228868</v>
-      </c>
-      <c r="B404" s="10" t="s">
-        <v>426</v>
+        <v>302253</v>
+      </c>
+      <c r="B404" s="12" t="s">
+        <v>425</v>
       </c>
       <c r="C404" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D404" s="6" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
     </row>
     <row r="405" spans="1:4">
       <c r="A405" s="9">
-        <v>283746</v>
+        <v>287546</v>
       </c>
       <c r="B405" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C405" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D405" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="406" spans="1:4">
       <c r="A406" s="9">
-        <v>287546</v>
+        <v>207160</v>
       </c>
       <c r="B406" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="C406" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D406" s="6" t="s">
         <v>428</v>
-      </c>
-      <c r="C406" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D406" s="6" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="407" spans="1:4">
       <c r="A407" s="9">
-        <v>289564</v>
+        <v>257631</v>
       </c>
       <c r="B407" s="10" t="s">
         <v>429</v>
@@ -8266,12 +8322,12 @@
         <v>8</v>
       </c>
       <c r="D407" s="6" t="s">
-        <v>395</v>
+        <v>428</v>
       </c>
     </row>
     <row r="408" spans="1:4">
       <c r="A408" s="9">
-        <v>289949</v>
+        <v>275241</v>
       </c>
       <c r="B408" s="10" t="s">
         <v>430</v>
@@ -8280,49 +8336,49 @@
         <v>13</v>
       </c>
       <c r="D408" s="6" t="s">
-        <v>395</v>
+        <v>428</v>
       </c>
     </row>
     <row r="409" spans="1:4">
-      <c r="A409" s="9">
-        <v>294884</v>
+      <c r="A409" s="9" t="s">
+        <v>431</v>
       </c>
       <c r="B409" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C409" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D409" s="6" t="s">
-        <v>395</v>
+        <v>420</v>
       </c>
     </row>
     <row r="410" spans="1:4">
       <c r="A410" s="9">
-        <v>257631</v>
+        <v>304230</v>
       </c>
       <c r="B410" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C410" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D410" s="6" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
     </row>
     <row r="411" spans="1:4">
       <c r="A411" s="9">
-        <v>275241</v>
+        <v>308642</v>
       </c>
       <c r="B411" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C411" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D411" s="6" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -8330,17 +8386,115 @@
         <v>305448</v>
       </c>
       <c r="B412" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C412" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D412" s="6" t="s">
-        <v>395</v>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4">
+      <c r="A413" s="9">
+        <v>211517</v>
+      </c>
+      <c r="B413" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="C413" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D413" s="6" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4">
+      <c r="A414" s="9">
+        <v>298837</v>
+      </c>
+      <c r="B414" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="C414" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D414" s="6" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
+      <c r="A415" s="9">
+        <v>298841</v>
+      </c>
+      <c r="B415" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="C415" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D415" s="6" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4">
+      <c r="A416" s="9">
+        <v>273276</v>
+      </c>
+      <c r="B416" s="10" t="s">
+        <v>439</v>
+      </c>
+      <c r="C416" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D416" s="6" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4">
+      <c r="A417" s="9">
+        <v>294614</v>
+      </c>
+      <c r="B417" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="C417" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D417" s="6" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4">
+      <c r="A418" s="9">
+        <v>302684</v>
+      </c>
+      <c r="B418" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="C418" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D418" s="6" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="419" ht="28" spans="1:4">
+      <c r="A419" s="9">
+        <v>329393</v>
+      </c>
+      <c r="B419" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="C419" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D419" s="6" t="s">
+        <v>428</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B32 B44 B98 B175:B176 B39:B40 B49 B46:B47 B36:B37 B165 B279 B167:B168 B188:B194 B291 B243:B245 B89 B148:B153 B100:B101 B110:B138 B171 B350:B351 B315 B141:B143 B208:B211 B323 B220:B229 B267:B269 B326:B327 B282:B284 B108 B78:B83 B231:B234 B329:B330 B272 B236:B238 B218 B413:B1048576 B341 B308:B309 B301 B160:B163 B180 B156:B157 B85:B86 B106 B286:B287 B216 B337:B338 B214 B53:B75 B51 B317:B320 B203 B332 B311 B293:B294 B298 B303:B304 B296 B249:B256">
+  <conditionalFormatting sqref="B$1:B$1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/template/机组花名册.xlsx
+++ b/public/template/机组花名册.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="469">
   <si>
     <t>员工号</t>
   </si>
@@ -1403,6 +1403,42 @@
   </si>
   <si>
     <t>WILLIAMS NICOLAS FRASER</t>
+  </si>
+  <si>
+    <t>刘先辉</t>
+  </si>
+  <si>
+    <t>秦智超</t>
+  </si>
+  <si>
+    <t>屈盟浩</t>
+  </si>
+  <si>
+    <t>李著</t>
+  </si>
+  <si>
+    <t>李宇航</t>
+  </si>
+  <si>
+    <t>张旭聪</t>
+  </si>
+  <si>
+    <t>邓昌民</t>
+  </si>
+  <si>
+    <t>王帅</t>
+  </si>
+  <si>
+    <t>王雍霏</t>
+  </si>
+  <si>
+    <t>王伟</t>
+  </si>
+  <si>
+    <t>田佳雨</t>
+  </si>
+  <si>
+    <t>刘峰</t>
   </si>
 </sst>
 </file>
@@ -2683,7 +2719,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q420"/>
+  <dimension ref="A1:Q432"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="15.6272727272727" style="1" customWidth="1"/>
@@ -17361,6 +17397,102 @@
       <c r="P420" s="8"/>
       <c r="Q420" s="8"/>
     </row>
+    <row r="421" spans="1:17">
+      <c r="A421" s="1">
+        <v>281274</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="422" spans="1:17">
+      <c r="A422" s="1">
+        <v>613081</v>
+      </c>
+      <c r="B422" s="1" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="423" spans="1:17">
+      <c r="A423" s="1">
+        <v>301003</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="424" spans="1:17">
+      <c r="A424" s="1">
+        <v>301881</v>
+      </c>
+      <c r="B424" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="425" spans="1:17">
+      <c r="A425" s="1">
+        <v>304621</v>
+      </c>
+      <c r="B425" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="426" spans="1:17">
+      <c r="A426" s="1">
+        <v>304017</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="427" spans="1:17">
+      <c r="A427" s="1">
+        <v>305195</v>
+      </c>
+      <c r="B427" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="428" spans="1:17">
+      <c r="A428" s="1">
+        <v>208960</v>
+      </c>
+      <c r="B428" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="429" spans="1:17">
+      <c r="A429" s="1">
+        <v>901672</v>
+      </c>
+      <c r="B429" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="430" spans="1:17">
+      <c r="A430" s="1">
+        <v>901662</v>
+      </c>
+      <c r="B430" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="431" spans="1:17">
+      <c r="A431" s="1">
+        <v>904779</v>
+      </c>
+      <c r="B431" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="432" spans="1:17">
+      <c r="A432" s="1">
+        <v>186645</v>
+      </c>
+      <c r="B432" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B54">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
